--- a/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0001T0006Z000C1N23_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0001T0006Z000C1N23_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>53.5941792951256</v>
+        <v>8.70905413545791</v>
       </c>
       <c r="D2" t="n">
-        <v>53.2043071441438</v>
+        <v>8.645699910923367</v>
       </c>
       <c r="E2" t="n">
-        <v>11.1939944481586</v>
+        <v>1.819024097825773</v>
       </c>
       <c r="F2" t="n">
-        <v>11.32457597818463</v>
+        <v>1.840243596455001</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>31.20619039880839</v>
+        <v>5.071005939806364</v>
       </c>
       <c r="D3" t="n">
-        <v>30.55515518777455</v>
+        <v>4.965212718013365</v>
       </c>
       <c r="E3" t="n">
-        <v>11.1939944481586</v>
+        <v>1.819024097825773</v>
       </c>
       <c r="F3" t="n">
-        <v>11.32457597818463</v>
+        <v>1.840243596455001</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
